--- a/xlsx/site.xlsx
+++ b/xlsx/site.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Icelab\JCIE\Online\JCIE_Website\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D466EF5C-BFA3-46A4-9340-A2E021C28EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE337913-D72C-4019-A453-F3B451A4DD80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1010" yWindow="1370" windowWidth="21600" windowHeight="13270" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="people" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="projects" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">people!$A$1:$O$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">people!$A$1:$O$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">projects!$A$1:$K$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">publications!$A$1:$I$18</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="276">
   <si>
     <t>id</t>
   </si>
@@ -383,15 +383,6 @@
     <t>dac-2025-exploiting;dac-2026-openacmv2;iseda-2026-portable</t>
   </si>
   <si>
-    <t>tang-haohao</t>
-  </si>
-  <si>
-    <t>Tang Haohao</t>
-  </si>
-  <si>
-    <t>唐浩浩</t>
-  </si>
-  <si>
     <t>wei</t>
   </si>
   <si>
@@ -470,15 +461,6 @@
     <t>徐一鹏</t>
   </si>
   <si>
-    <t>yuan-yizhong</t>
-  </si>
-  <si>
-    <t>Yuan Yizhong</t>
-  </si>
-  <si>
-    <t>苑艺钟</t>
-  </si>
-  <si>
     <t>zexi-zhu</t>
   </si>
   <si>
@@ -805,29 +787,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>汪睿涵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ruihan Wang</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ruihan-wang</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>彭林海</t>
-  </si>
-  <si>
-    <t>Linhai Peng</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>linhai-peng</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>张哲</t>
   </si>
   <si>
@@ -872,13 +831,67 @@
   <si>
     <t>/people/none.jpg</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>homepage_url</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scholar_url</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>github_url</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?user=AB5z_AkAAAAJ&amp;hl=en</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://wxing.me/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cover</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/projects/proj-2.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/projects/proj-3.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/projects/proj-1.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/projects/proj-4.jpg</t>
+  </si>
+  <si>
+    <t>/projects/proj-5.jpg</t>
+  </si>
+  <si>
+    <t>/projects/proj-6.jpg</t>
+  </si>
+  <si>
+    <t>/projects/proj-7.jpg</t>
+  </si>
+  <si>
+    <t>/projects/proj-8.jpg</t>
+  </si>
+  <si>
+    <t>/projects/proj-9.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -917,6 +930,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -935,10 +956,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -948,9 +970,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1250,13 +1274,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1303,10 +1327,19 @@
         <v>84</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>85</v>
       </c>
@@ -1323,16 +1356,16 @@
         <v>2024</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>87</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>88</v>
       </c>
@@ -1349,16 +1382,16 @@
         <v>2025</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>89</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>90</v>
       </c>
@@ -1375,7 +1408,7 @@
         <v>2022</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>93</v>
@@ -1393,10 +1426,10 @@
         <v>1</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>97</v>
       </c>
@@ -1419,10 +1452,10 @@
         <v>99</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>100</v>
       </c>
@@ -1439,13 +1472,13 @@
         <v>2024</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>101</v>
       </c>
@@ -1465,10 +1498,10 @@
         <v>104</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>105</v>
       </c>
@@ -1485,16 +1518,16 @@
         <v>2025</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>106</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>107</v>
       </c>
@@ -1511,13 +1544,13 @@
         <v>2026</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>110</v>
       </c>
@@ -1534,13 +1567,13 @@
         <v>2026</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>113</v>
       </c>
@@ -1557,13 +1590,13 @@
         <v>2026</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>116</v>
       </c>
@@ -1580,132 +1613,138 @@
         <v>2025</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>117</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q13" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="R13" s="5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="G13" s="3">
-        <v>2026</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="C14" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
+      </c>
+      <c r="G14" s="3">
+        <v>2022</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>129</v>
+        <v>260</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>132</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O14" s="3">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>86</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G15" s="3">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>135</v>
+        <v>260</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="O15" s="3">
-        <v>3</v>
+        <v>137</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>86</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G16" s="3">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -1722,13 +1761,13 @@
         <v>143</v>
       </c>
       <c r="G17" s="3">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -1748,155 +1787,155 @@
         <v>2026</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>272</v>
+        <v>147</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>86</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G19" s="3">
         <v>2026</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>86</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G20" s="3">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>153</v>
+        <v>260</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O20" s="3">
+        <v>4</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>86</v>
+        <v>244</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G21" s="3">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>272</v>
+        <v>260</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O21" s="3">
+        <v>2</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>157</v>
+        <v>245</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>86</v>
+        <v>244</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>158</v>
+        <v>243</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>159</v>
+        <v>242</v>
       </c>
       <c r="G22" s="3">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="O22" s="3">
-        <v>4</v>
+        <v>260</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>163</v>
+        <v>248</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>165</v>
+        <v>247</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>246</v>
       </c>
       <c r="G23" s="3">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="O23" s="3">
-        <v>2</v>
+        <v>260</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -1904,45 +1943,45 @@
         <v>251</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="4" t="s">
         <v>249</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>248</v>
       </c>
       <c r="G24" s="3">
         <v>2026</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>252</v>
       </c>
       <c r="G25" s="3">
         <v>2026</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
@@ -1950,119 +1989,31 @@
         <v>257</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>255</v>
+      <c r="D26" s="2" t="s">
+        <v>252</v>
       </c>
       <c r="G26" s="3">
         <v>2026</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="G27" s="3">
-        <v>2026</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="G28" s="3">
-        <v>2026</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="P28" s="3" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="G29" s="3">
-        <v>2026</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G30" s="3">
-        <v>2026</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="P30" s="3" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O23" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:O21" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="R13" r:id="rId1" xr:uid="{01DDBAAE-E05C-44DD-A1D1-DAC8B1111C51}"/>
+    <hyperlink ref="Q13" r:id="rId2" xr:uid="{CBE8AD3D-13C9-40BA-AE97-168CC9786284}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2077,39 +2028,39 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
       </c>
       <c r="F1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="I1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B2" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C2" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D2">
         <v>2026</v>
@@ -2118,10 +2069,10 @@
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -2129,10 +2080,10 @@
         <v>99</v>
       </c>
       <c r="B3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D3">
         <v>2026</v>
@@ -2141,7 +2092,7 @@
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="G3" t="s">
         <v>22</v>
@@ -2152,10 +2103,10 @@
         <v>89</v>
       </c>
       <c r="B4" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C4" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D4">
         <v>2026</v>
@@ -2164,7 +2115,7 @@
         <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="G4" t="s">
         <v>22</v>
@@ -2172,13 +2123,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B5" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C5" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D5">
         <v>2026</v>
@@ -2187,7 +2138,7 @@
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G5" t="s">
         <v>22</v>
@@ -2195,13 +2146,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B6" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C6" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D6">
         <v>2025</v>
@@ -2210,10 +2161,10 @@
         <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="G6" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -2221,10 +2172,10 @@
         <v>87</v>
       </c>
       <c r="B7" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C7" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D7">
         <v>2025</v>
@@ -2233,21 +2184,21 @@
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="G7" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B8" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C8" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D8">
         <v>2025</v>
@@ -2256,21 +2207,21 @@
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="G8" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B9" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C9" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D9">
         <v>2025</v>
@@ -2279,21 +2230,21 @@
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="G9" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B10" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C10" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D10">
         <v>2025</v>
@@ -2302,21 +2253,21 @@
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G10" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B11" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C11" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D11">
         <v>2025</v>
@@ -2325,21 +2276,21 @@
         <v>37</v>
       </c>
       <c r="F11" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="G11" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B12" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C12" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D12">
         <v>2024</v>
@@ -2348,21 +2299,21 @@
         <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="G12" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B13" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C13" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D13">
         <v>2024</v>
@@ -2371,21 +2322,21 @@
         <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="G13" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B14" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C14" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D14">
         <v>2024</v>
@@ -2394,21 +2345,21 @@
         <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="G14" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B15" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C15" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D15">
         <v>2023</v>
@@ -2417,21 +2368,21 @@
         <v>12</v>
       </c>
       <c r="F15" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="G15" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B16" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C16" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D16">
         <v>2023</v>
@@ -2440,21 +2391,21 @@
         <v>12</v>
       </c>
       <c r="F16" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="G16" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B17" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C17" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D17">
         <v>2023</v>
@@ -2463,21 +2414,21 @@
         <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="G17" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B18" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C18" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D18">
         <v>2023</v>
@@ -2486,10 +2437,10 @@
         <v>12</v>
       </c>
       <c r="F18" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G18" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -2501,10 +2452,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2538,8 +2489,11 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -2570,8 +2524,11 @@
       <c r="J2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -2602,8 +2559,11 @@
       <c r="J3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -2634,8 +2594,11 @@
       <c r="J4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -2666,8 +2629,11 @@
       <c r="J5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -2698,8 +2664,11 @@
       <c r="J6" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>49</v>
       </c>
@@ -2730,8 +2699,11 @@
       <c r="J7" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>54</v>
       </c>
@@ -2762,8 +2734,11 @@
       <c r="J8" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>61</v>
       </c>
@@ -2794,8 +2769,11 @@
       <c r="J9" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>68</v>
       </c>
@@ -2825,6 +2803,9 @@
       </c>
       <c r="J10" t="s">
         <v>72</v>
+      </c>
+      <c r="L10" t="s">
+        <v>275</v>
       </c>
     </row>
   </sheetData>
